--- a/public/downloads/StreibelMicrokinetic2021.xlsx
+++ b/public/downloads/StreibelMicrokinetic2021.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CH3CHCH2</t>
@@ -656,10 +679,10 @@
         <v>4</v>
       </c>
       <c r="N3" s="5">
-        <v>169.8808305263519</v>
+        <v>169880.8305263519</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03248820625862534</v>
+        <v>32.48820625862534</v>
       </c>
       <c r="P3" s="5">
         <v>5229</v>
@@ -706,10 +729,10 @@
         <v>4</v>
       </c>
       <c r="N4" s="5">
-        <v>45.64697194099426</v>
+        <v>45646.97194099426</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04967026326549974</v>
+        <v>49.67026326549974</v>
       </c>
       <c r="P4" s="5">
         <v>919</v>
@@ -756,10 +779,10 @@
         <v>4</v>
       </c>
       <c r="N5" s="5">
-        <v>118.954826593399</v>
+        <v>118954.826593399</v>
       </c>
       <c r="O5" s="4">
-        <v>0.2332447580262726</v>
+        <v>233.2447580262726</v>
       </c>
       <c r="P5" s="5">
         <v>510</v>
@@ -806,10 +829,10 @@
         <v>4</v>
       </c>
       <c r="N6" s="5">
-        <v>546.8660161495209</v>
+        <v>546866.0161495209</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08373388702335337</v>
+        <v>83.73388702335336</v>
       </c>
       <c r="P6" s="5">
         <v>6531</v>
@@ -856,10 +879,10 @@
         <v>4</v>
       </c>
       <c r="N7" s="5">
-        <v>67.49346733093262</v>
+        <v>67493.46733093262</v>
       </c>
       <c r="O7" s="4">
-        <v>0.173060172643417</v>
+        <v>173.060172643417</v>
       </c>
       <c r="P7" s="5">
         <v>390</v>
@@ -906,10 +929,10 @@
         <v>4</v>
       </c>
       <c r="N8" s="5">
-        <v>6.95845365524292</v>
+        <v>6958.45365524292</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01356423714472304</v>
+        <v>13.56423714472304</v>
       </c>
       <c r="P8" s="5">
         <v>513</v>
@@ -956,10 +979,10 @@
         <v>4</v>
       </c>
       <c r="N9" s="5">
-        <v>19.24996852874756</v>
+        <v>19249.96852874756</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02993774265746121</v>
+        <v>29.93774265746121</v>
       </c>
       <c r="P9" s="5">
         <v>643</v>
@@ -1006,10 +1029,10 @@
         <v>4</v>
       </c>
       <c r="N10" s="5">
-        <v>40.50502347946167</v>
+        <v>40505.02347946167</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08491619178084207</v>
+        <v>84.91619178084207</v>
       </c>
       <c r="P10" s="5">
         <v>477</v>
@@ -1056,10 +1079,10 @@
         <v>4</v>
       </c>
       <c r="N11" s="5">
-        <v>25.33610248565674</v>
+        <v>25336.10248565674</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04021603569151863</v>
+        <v>40.21603569151863</v>
       </c>
       <c r="P11" s="5">
         <v>630</v>
@@ -1106,10 +1129,10 @@
         <v>4</v>
       </c>
       <c r="N12" s="5">
-        <v>8.498018026351929</v>
+        <v>8498.018026351929</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01918288493533167</v>
+        <v>19.18288493533167</v>
       </c>
       <c r="P12" s="5">
         <v>443</v>
@@ -1156,10 +1179,10 @@
         <v>4</v>
       </c>
       <c r="N13" s="5">
-        <v>28.89454960823059</v>
+        <v>28894.54960823059</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07241741756448769</v>
+        <v>72.41741756448769</v>
       </c>
       <c r="P13" s="5">
         <v>399</v>
@@ -1206,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="N14" s="5">
-        <v>46.34995937347412</v>
+        <v>46349.95937347412</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2305968128033538</v>
+        <v>230.5968128033538</v>
       </c>
       <c r="P14" s="5">
         <v>201</v>
@@ -1256,10 +1279,10 @@
         <v>4</v>
       </c>
       <c r="N15" s="5">
-        <v>98.62755036354065</v>
+        <v>98627.55036354065</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2331620575970228</v>
+        <v>233.1620575970228</v>
       </c>
       <c r="P15" s="5">
         <v>423</v>
@@ -1306,10 +1329,10 @@
         <v>4</v>
       </c>
       <c r="N16" s="5">
-        <v>24.99386930465698</v>
+        <v>24993.86930465698</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09918202105022612</v>
+        <v>99.18202105022613</v>
       </c>
       <c r="P16" s="5">
         <v>252</v>
@@ -1356,10 +1379,10 @@
         <v>4</v>
       </c>
       <c r="N17" s="5">
-        <v>48.45825052261353</v>
+        <v>48458.25052261353</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09614732246550303</v>
+        <v>96.14732246550304</v>
       </c>
       <c r="P17" s="5">
         <v>504</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,25 +1494,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1064801368926211</v>
+        <v>0.3397740928983737</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1064801368926211</v>
+        <v>0.3397740928983737</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1438987288391509</v>
+        <v>0.2553843791952808</v>
       </c>
       <c r="E3" s="4">
-        <v>77.14285714285714</v>
+        <v>69.28571428571429</v>
       </c>
       <c r="F3" s="4">
-        <v>84.46308724832215</v>
+        <v>73.23825503355705</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -1498,25 +1553,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3397740928983737</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3397740928983737</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4359492790191979</v>
+        <v>0.3526789132160957</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4359492790191979</v>
+        <v>0.3526789132160957</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6027803071843323</v>
+        <v>0.3950157984198768</v>
       </c>
       <c r="E4" s="4">
-        <v>81.32653061224489</v>
+        <v>88.46938775510205</v>
       </c>
       <c r="F4" s="4">
-        <v>85.33557046979865</v>
+        <v>87.85234899328859</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -1539,9 +1610,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3526789132160957</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3526789132160957</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1639,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1647,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1658,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1700,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,25 +1731,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.480350065507082</v>
+        <v>1.096950102128176</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3508644852554426</v>
+        <v>0.7954483780777082</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2391667634983605</v>
+        <v>0.6923327925578633</v>
       </c>
       <c r="E3" s="4">
-        <v>62.90816326530612</v>
+        <v>66.00340136054422</v>
       </c>
       <c r="F3" s="4">
-        <v>69.84899328859061</v>
+        <v>69.62527964205816</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -1656,48 +1776,64 @@
         <v>1</v>
       </c>
       <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.096950102128176</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7954483780777082</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2471512385964161</v>
+        <v>1.349385125315166</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2471512385964161</v>
+        <v>1.184498197821085</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1772217511024792</v>
+        <v>0.4814041682839161</v>
       </c>
       <c r="E4" s="4">
-        <v>86.78571428571429</v>
+        <v>81.12244897959184</v>
       </c>
       <c r="F4" s="4">
-        <v>87.36577181208054</v>
+        <v>67.98657718120805</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1711,9 +1847,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.349385125315166</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.184498197821085</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1876,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1884,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1895,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1937,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,25 +1968,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4346451279743633</v>
+        <v>0.1064801368926211</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4346451279743633</v>
+        <v>0.1064801368926211</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3570560929401836</v>
+        <v>0.1438987288391509</v>
       </c>
       <c r="E3" s="4">
-        <v>80.66326530612245</v>
+        <v>77.14285714285714</v>
       </c>
       <c r="F3" s="4">
-        <v>86.24720357941831</v>
+        <v>84.46308724832215</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -1842,25 +2027,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1064801368926211</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1064801368926211</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1452374218788464</v>
+        <v>0.4359492790191979</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1452374218788464</v>
+        <v>0.4359492790191979</v>
       </c>
       <c r="D4" s="4">
-        <v>0.32077357757953</v>
+        <v>0.6027803071843323</v>
       </c>
       <c r="E4" s="4">
-        <v>85.30612244897959</v>
+        <v>81.32653061224489</v>
       </c>
       <c r="F4" s="4">
-        <v>87.69574944071589</v>
+        <v>85.33557046979865</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -1883,9 +2084,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4359492790191979</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4359492790191979</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2113,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2121,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2132,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2174,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,34 +2205,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4038615706340352</v>
+        <v>0.480350065507082</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4038615706340352</v>
+        <v>0.3508644852554426</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4058642866984883</v>
+        <v>0.2391667634983605</v>
       </c>
       <c r="E3" s="4">
-        <v>81.68367346938776</v>
+        <v>62.90816326530612</v>
       </c>
       <c r="F3" s="4">
-        <v>84.86577181208054</v>
+        <v>69.84899328859061</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2014,25 +2264,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.480350065507082</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3508644852554426</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3142593928932911</v>
+        <v>0.2471512385964161</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3142593928932911</v>
+        <v>0.2471512385964161</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3034634350624401</v>
+        <v>0.1772217511024792</v>
       </c>
       <c r="E4" s="4">
         <v>86.78571428571429</v>
       </c>
       <c r="F4" s="4">
-        <v>87.86912751677852</v>
+        <v>87.36577181208054</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -2055,9 +2321,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2471512385964161</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2471512385964161</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2350,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2358,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2369,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2411,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,25 +2442,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4267918583973938</v>
+        <v>0.4346451279743633</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4267918583973938</v>
+        <v>0.4346451279743633</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3993374821766906</v>
+        <v>0.3570560929401836</v>
       </c>
       <c r="E3" s="4">
-        <v>95.15306122448979</v>
+        <v>80.66326530612245</v>
       </c>
       <c r="F3" s="4">
-        <v>95.85570469798658</v>
+        <v>86.24720357941831</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2186,37 +2501,53 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4346451279743633</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4346451279743633</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>2.194153523334535</v>
+        <v>0.1452374218788464</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.1452374218788464</v>
       </c>
       <c r="D4" s="4">
-        <v>2.271642660984071</v>
+        <v>0.32077357757953</v>
       </c>
       <c r="E4" s="4">
-        <v>95.30612244897959</v>
+        <v>85.30612244897959</v>
       </c>
       <c r="F4" s="4">
-        <v>96.15771812080537</v>
+        <v>87.69574944071589</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2225,11 +2556,27 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1452374218788464</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1452374218788464</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2587,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2595,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2606,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2648,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,25 +2679,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2112384322062617</v>
+        <v>0.4038615706340352</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2112384322062617</v>
+        <v>0.4038615706340352</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3218265059367305</v>
+        <v>0.4058642866984883</v>
       </c>
       <c r="E3" s="4">
-        <v>80.66326530612245</v>
+        <v>81.68367346938776</v>
       </c>
       <c r="F3" s="4">
-        <v>87.85234899328859</v>
+        <v>84.86577181208054</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2358,25 +2738,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4038615706340352</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4038615706340352</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.656589007267002</v>
+        <v>0.3142593928932911</v>
       </c>
       <c r="C4" s="4">
-        <v>1.656589007267002</v>
+        <v>0.3142593928932911</v>
       </c>
       <c r="D4" s="4">
-        <v>1.932894682773622</v>
+        <v>0.3034634350624401</v>
       </c>
       <c r="E4" s="4">
-        <v>84.59183673469387</v>
+        <v>86.78571428571429</v>
       </c>
       <c r="F4" s="4">
-        <v>89.98322147651007</v>
+        <v>87.86912751677852</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -2399,9 +2795,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3142593928932911</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3142593928932911</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2824,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2832,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2843,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2885,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,25 +2916,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4477490899190002</v>
+        <v>0.4267918583973938</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4477490899190002</v>
+        <v>0.4267918583973938</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4248954770192199</v>
+        <v>0.3993374821766906</v>
       </c>
       <c r="E3" s="4">
-        <v>94.48979591836735</v>
+        <v>95.15306122448979</v>
       </c>
       <c r="F3" s="4">
-        <v>95.35234899328859</v>
+        <v>95.85570469798658</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2530,37 +2975,51 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4267918583973938</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4267918583973938</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.121486401447328</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.121486401447328</v>
-      </c>
+        <v>2.194153523334535</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>1.163546419033054</v>
+        <v>2.271642660984071</v>
       </c>
       <c r="E4" s="4">
-        <v>94.03061224489795</v>
+        <v>95.30612244897959</v>
       </c>
       <c r="F4" s="4">
-        <v>94.02684563758389</v>
+        <v>96.15771812080537</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
@@ -2569,11 +3028,25 @@
         <v>0</v>
       </c>
       <c r="M4" s="5">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>2.194153523334535</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3057,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3065,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3076,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3118,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,25 +3149,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.411169004164602</v>
+        <v>0.2112384322062617</v>
       </c>
       <c r="C3" s="4">
-        <v>1.411169004164602</v>
+        <v>0.2112384322062617</v>
       </c>
       <c r="D3" s="4">
-        <v>1.333329629622337</v>
+        <v>0.3218265059367305</v>
       </c>
       <c r="E3" s="4">
-        <v>76.4795918367347</v>
+        <v>80.66326530612245</v>
       </c>
       <c r="F3" s="4">
-        <v>83.97651006711409</v>
+        <v>87.85234899328859</v>
       </c>
       <c r="G3" s="5">
         <v>2</v>
@@ -2702,25 +3208,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2112384322062617</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2112384322062617</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.271353220828985</v>
+        <v>1.656589007267002</v>
       </c>
       <c r="C4" s="4">
-        <v>1.271353220828985</v>
+        <v>1.656589007267002</v>
       </c>
       <c r="D4" s="4">
-        <v>1.531492686160988</v>
+        <v>1.932894682773622</v>
       </c>
       <c r="E4" s="4">
-        <v>83.67346938775511</v>
+        <v>84.59183673469387</v>
       </c>
       <c r="F4" s="4">
-        <v>89.32885906040268</v>
+        <v>89.98322147651007</v>
       </c>
       <c r="G4" s="5">
         <v>2</v>
@@ -2743,9 +3265,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.656589007267002</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.656589007267002</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3294,1344 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4477490899190002</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4477490899190002</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4248954770192199</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.48979591836735</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.35234899328859</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4477490899190002</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4477490899190002</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.121486401447328</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.121486401447328</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.163546419033054</v>
+      </c>
+      <c r="E4" s="4">
+        <v>94.03061224489795</v>
+      </c>
+      <c r="F4" s="4">
+        <v>94.02684563758389</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.121486401447328</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.121486401447328</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.411169004164602</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.411169004164602</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.333329629622337</v>
+      </c>
+      <c r="E3" s="4">
+        <v>76.4795918367347</v>
+      </c>
+      <c r="F3" s="4">
+        <v>83.97651006711409</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.411169004164602</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.411169004164602</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.271353220828985</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.271353220828985</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.531492686160988</v>
+      </c>
+      <c r="E4" s="4">
+        <v>83.67346938775511</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.32885906040268</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.271353220828985</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>1.271353220828985</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>50</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>50</v>
+      </c>
+      <c r="E3" s="3">
+        <v>50</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.5216420617707627</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.5762647133888095</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.5847396970621048</v>
+      </c>
+      <c r="K3" s="4">
+        <v>78.27380952380955</v>
+      </c>
+      <c r="L3" s="4">
+        <v>68.40324384787476</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="5">
+        <v>169880.8305263519</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.48820625862534</v>
+      </c>
+      <c r="P3" s="5">
+        <v>5229</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>75</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.8964738965860306</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.7155624129930706</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.8905782819620072</v>
+      </c>
+      <c r="K4" s="4">
+        <v>70.25510204081631</v>
+      </c>
+      <c r="L4" s="4">
+        <v>73.71923937360056</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="5">
+        <v>45646.97194099426</v>
+      </c>
+      <c r="O4" s="4">
+        <v>49.67026326549974</v>
+      </c>
+      <c r="P4" s="5">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1313435797474085</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1313435797474085</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2565678832015692</v>
+      </c>
+      <c r="K5" s="4">
+        <v>82.21938775510205</v>
+      </c>
+      <c r="L5" s="4">
+        <v>86.10738255033557</v>
+      </c>
+      <c r="M5" s="5">
+        <v>4</v>
+      </c>
+      <c r="N5" s="5">
+        <v>118954.826593399</v>
+      </c>
+      <c r="O5" s="4">
+        <v>233.2447580262726</v>
+      </c>
+      <c r="P5" s="5">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>50</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>50</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.6074926411874912</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.4797737411354319</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.5090737702394108</v>
+      </c>
+      <c r="K6" s="4">
+        <v>81.00340136054423</v>
+      </c>
+      <c r="L6" s="4">
+        <v>76.68344519015659</v>
+      </c>
+      <c r="M6" s="5">
+        <v>4</v>
+      </c>
+      <c r="N6" s="5">
+        <v>546866.0161495209</v>
+      </c>
+      <c r="O6" s="4">
+        <v>83.73388702335336</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6531</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.3101901648497005</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3101901648497005</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.4030766501837206</v>
+      </c>
+      <c r="K7" s="4">
+        <v>86.93877551020408</v>
+      </c>
+      <c r="L7" s="4">
+        <v>90.72986577181209</v>
+      </c>
+      <c r="M7" s="5">
+        <v>4</v>
+      </c>
+      <c r="N7" s="5">
+        <v>67493.46733093262</v>
+      </c>
+      <c r="O7" s="4">
+        <v>173.060172643417</v>
+      </c>
+      <c r="P7" s="5">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3462265030572347</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.3462265030572347</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.3252000888075788</v>
+      </c>
+      <c r="K8" s="4">
+        <v>78.87755102040816</v>
+      </c>
+      <c r="L8" s="4">
+        <v>80.54530201342281</v>
+      </c>
+      <c r="M8" s="5">
+        <v>4</v>
+      </c>
+      <c r="N8" s="5">
+        <v>6958.45365524292</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13.56423714472304</v>
+      </c>
+      <c r="P8" s="5">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>25</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1.223167613721671</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.9899732879493968</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.5868684804208897</v>
+      </c>
+      <c r="K9" s="4">
+        <v>73.56292517006801</v>
+      </c>
+      <c r="L9" s="4">
+        <v>68.80592841163309</v>
+      </c>
+      <c r="M9" s="5">
+        <v>4</v>
+      </c>
+      <c r="N9" s="5">
+        <v>19249.96852874756</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.93774265746121</v>
+      </c>
+      <c r="P9" s="5">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.2712147079559095</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2712147079559095</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3733395180117416</v>
+      </c>
+      <c r="K10" s="4">
+        <v>79.23469387755102</v>
+      </c>
+      <c r="L10" s="4">
+        <v>84.8993288590604</v>
+      </c>
+      <c r="M10" s="5">
+        <v>4</v>
+      </c>
+      <c r="N10" s="5">
+        <v>40505.02347946167</v>
+      </c>
+      <c r="O10" s="4">
+        <v>84.91619178084207</v>
+      </c>
+      <c r="P10" s="5">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>75</v>
+      </c>
+      <c r="C11" s="3">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3637506520517491</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2817223208160916</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2081942573004198</v>
+      </c>
+      <c r="K11" s="4">
+        <v>74.84693877551021</v>
+      </c>
+      <c r="L11" s="4">
+        <v>78.60738255033557</v>
+      </c>
+      <c r="M11" s="5">
+        <v>4</v>
+      </c>
+      <c r="N11" s="5">
+        <v>25336.10248565674</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.21603569151863</v>
+      </c>
+      <c r="P11" s="5">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2899412749266048</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2899412749266048</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.3389148352598568</v>
+      </c>
+      <c r="K12" s="4">
+        <v>82.98469387755102</v>
+      </c>
+      <c r="L12" s="4">
+        <v>86.97147651006713</v>
+      </c>
+      <c r="M12" s="5">
+        <v>4</v>
+      </c>
+      <c r="N12" s="5">
+        <v>8498.018026351929</v>
+      </c>
+      <c r="O12" s="4">
+        <v>19.18288493533167</v>
+      </c>
+      <c r="P12" s="5">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.3590604817636631</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.3590604817636631</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.3546638608804642</v>
+      </c>
+      <c r="K13" s="4">
+        <v>84.23469387755102</v>
+      </c>
+      <c r="L13" s="4">
+        <v>86.36744966442953</v>
+      </c>
+      <c r="M13" s="5">
+        <v>4</v>
+      </c>
+      <c r="N13" s="5">
+        <v>28894.54960823059</v>
+      </c>
+      <c r="O13" s="4">
+        <v>72.41741756448769</v>
+      </c>
+      <c r="P13" s="5">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>50</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>50</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.310472690865964</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.4267918583973938</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1.335490071580381</v>
+      </c>
+      <c r="K14" s="4">
+        <v>95.2295918367347</v>
+      </c>
+      <c r="L14" s="4">
+        <v>96.00671140939598</v>
+      </c>
+      <c r="M14" s="5">
+        <v>4</v>
+      </c>
+      <c r="N14" s="5">
+        <v>46349.95937347412</v>
+      </c>
+      <c r="O14" s="4">
+        <v>230.5968128033538</v>
+      </c>
+      <c r="P14" s="5">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.9339137197366316</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.9339137197366316</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1.127360594355176</v>
+      </c>
+      <c r="K15" s="4">
+        <v>82.62755102040816</v>
+      </c>
+      <c r="L15" s="4">
+        <v>88.91778523489933</v>
+      </c>
+      <c r="M15" s="5">
+        <v>4</v>
+      </c>
+      <c r="N15" s="5">
+        <v>98627.55036354065</v>
+      </c>
+      <c r="O15" s="4">
+        <v>233.1620575970228</v>
+      </c>
+      <c r="P15" s="5">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.784617745683164</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.784617745683164</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.7942209480261369</v>
+      </c>
+      <c r="K16" s="4">
+        <v>94.26020408163265</v>
+      </c>
+      <c r="L16" s="4">
+        <v>94.68959731543625</v>
+      </c>
+      <c r="M16" s="5">
+        <v>4</v>
+      </c>
+      <c r="N16" s="5">
+        <v>24993.86930465698</v>
+      </c>
+      <c r="O16" s="4">
+        <v>99.18202105022613</v>
+      </c>
+      <c r="P16" s="5">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>1.341261112496793</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1.341261112496793</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.432411157891663</v>
+      </c>
+      <c r="K17" s="4">
+        <v>80.07653061224489</v>
+      </c>
+      <c r="L17" s="4">
+        <v>86.65268456375838</v>
+      </c>
+      <c r="M17" s="5">
+        <v>4</v>
+      </c>
+      <c r="N17" s="5">
+        <v>48458.25052261353</v>
+      </c>
+      <c r="O17" s="4">
+        <v>96.14732246550304</v>
+      </c>
+      <c r="P17" s="5">
+        <v>504</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2881,10 +4751,10 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3516,9 +5386,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>2</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>4</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>4</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>4</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6154,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6196,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,10 +6227,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.8244929793254414</v>
@@ -3629,10 +6286,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8244929793254414</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7417298111831769</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2187911442160839</v>
@@ -3670,9 +6343,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2187911442160839</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.410799615594442</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6372,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6391,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6433,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,10 +6464,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6512904646770039</v>
@@ -3801,10 +6523,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6512904646770039</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6512904646770039</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>1.141657328495057</v>
@@ -3842,9 +6580,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.141657328495057</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8441063096252037</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6609,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6628,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6670,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,10 +6701,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.0391851435379067</v>
@@ -3973,10 +6760,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0391851435379067</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0391851435379067</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2235020159569103</v>
@@ -4014,9 +6817,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2235020159569103</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2235020159569103</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6846,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6865,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6907,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,10 +6938,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3805385115520039</v>
@@ -4145,10 +6997,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3805385115520039</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3137245926773176</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.8344467708229786</v>
@@ -4186,9 +7054,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8344467708229786</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6458228895935463</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7083,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7102,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7144,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,10 +7175,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1857418534382305</v>
@@ -4317,10 +7234,26 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1857418534382305</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1857418534382305</v>
+      </c>
+      <c r="R3" s="5">
+        <v>2</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4346384762611706</v>
@@ -4358,9 +7291,25 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4346384762611706</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4346384762611706</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7320,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3397740928983737</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3397740928983737</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2553843791952808</v>
-      </c>
-      <c r="E3" s="4">
-        <v>69.28571428571429</v>
-      </c>
-      <c r="F3" s="4">
-        <v>73.23825503355705</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3526789132160957</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3526789132160957</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3950157984198768</v>
-      </c>
-      <c r="E4" s="4">
-        <v>88.46938775510205</v>
-      </c>
-      <c r="F4" s="4">
-        <v>87.85234899328859</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.096950102128176</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7954483780777082</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6923327925578633</v>
-      </c>
-      <c r="E3" s="4">
-        <v>66.00340136054422</v>
-      </c>
-      <c r="F3" s="4">
-        <v>69.62527964205816</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.349385125315166</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1.184498197821085</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4814041682839161</v>
-      </c>
-      <c r="E4" s="4">
-        <v>81.12244897959184</v>
-      </c>
-      <c r="F4" s="4">
-        <v>67.98657718120805</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
